--- a/_ForDRA/BVSimulationFiles/72.xlsx
+++ b/_ForDRA/BVSimulationFiles/72.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0007142857142857144</v>
+        <v>0.01428571428571429</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007223582867587268</v>
+        <v>0.01444716573517454</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007302115291114909</v>
+        <v>0.01460423058222982</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007378488943042406</v>
+        <v>0.01475697788608481</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007452737893491826</v>
+        <v>0.01490547578698365</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007524895758731874</v>
+        <v>0.01504979151746375</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007594995706739209</v>
+        <v>0.01518999141347842</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007663070462694894</v>
+        <v>0.01532614092538979</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007729152314416819</v>
+        <v>0.01545830462883364</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007793273117728701</v>
+        <v>0.0155865462354574</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007855464301766442</v>
+        <v>0.01571092860353288</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007915756874222512</v>
+        <v>0.01583151374844502</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007974181426529127</v>
+        <v>0.01594836285305825</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0008030768138980812</v>
+        <v>0.01606153627796162</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008085546785797122</v>
+        <v>0.01617109357159424</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0008138546740126137</v>
+        <v>0.01627709348025227</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0008189796978989464</v>
+        <v>0.01637959395797893</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008239326088169317</v>
+        <v>0.01647865217633863</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008287162267038423</v>
+        <v>0.01657432453407685</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0008333333333333334</v>
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0007142857142857144</v>
+        <v>0.01428571428571429</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0007223582867587268</v>
+        <v>0.01444716573517454</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007302115291114909</v>
+        <v>0.01460423058222982</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007378488943042406</v>
+        <v>0.01475697788608481</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007452737893491826</v>
+        <v>0.01490547578698365</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007524895758731874</v>
+        <v>0.01504979151746375</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007594995706739209</v>
+        <v>0.01518999141347842</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007663070462694894</v>
+        <v>0.01532614092538979</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007729152314416819</v>
+        <v>0.01545830462883364</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007793273117728701</v>
+        <v>0.0155865462354574</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007855464301766442</v>
+        <v>0.01571092860353288</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0007915756874222512</v>
+        <v>0.01583151374844502</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0007974181426529127</v>
+        <v>0.01594836285305825</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0008030768138980812</v>
+        <v>0.01606153627796162</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008085546785797122</v>
+        <v>0.01617109357159424</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0008138546740126137</v>
+        <v>0.01627709348025227</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008189796978989464</v>
+        <v>0.01637959395797893</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008239326088169317</v>
+        <v>0.01647865217633863</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008287162267038423</v>
+        <v>0.01657432453407685</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0008333333333333334</v>
+        <v>0.01666666666666667</v>
       </c>
     </row>
   </sheetData>
